--- a/artfynd/A 63108-2025 artfynd.xlsx
+++ b/artfynd/A 63108-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66327600</v>
+        <v>130982602</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Naturskog S Lill-Skarvhöjden, Renålandet, Ström, Jmt</t>
+          <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514072.7796777306</v>
+        <v>513918</v>
       </c>
       <c r="R2" t="n">
-        <v>7097652.679305307</v>
+        <v>7097881</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lockläte</t>
+          <t>Minst 1 fruktkropp i en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,75 +766,99 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96280730</v>
+        <v>130983968</v>
       </c>
       <c r="B3" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221343</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NA, Jmt</t>
+          <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513972.9882127888</v>
+        <v>513808</v>
       </c>
       <c r="R3" t="n">
-        <v>7097374.058470867</v>
+        <v>7097938</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +882,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 1 fruktkropp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,32 +901,59 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>En gammal grovbarkig skadad sälg.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea # En gammal grovbarkig skadad sälg.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Axelson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130983955</v>
+        <v>130983960</v>
       </c>
       <c r="B4" t="n">
-        <v>80351</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,28 +961,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -965,10 +992,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513615</v>
+        <v>513513</v>
       </c>
       <c r="R4" t="n">
-        <v>7098111</v>
+        <v>7098096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,6 +1043,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130983952</v>
+        <v>130983919</v>
       </c>
       <c r="B5" t="n">
-        <v>80351</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,26 +1086,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1117,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513911</v>
+        <v>513795</v>
       </c>
       <c r="R5" t="n">
-        <v>7097913</v>
+        <v>7097973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,22 +1172,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1159,37 +1205,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130983942</v>
+        <v>130983929</v>
       </c>
       <c r="B6" t="n">
-        <v>80351</v>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1197,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513807</v>
+        <v>513914</v>
       </c>
       <c r="R6" t="n">
-        <v>7097941</v>
+        <v>7097909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,6 +1298,21 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1265,39 +1330,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130982570</v>
+        <v>130983930</v>
       </c>
       <c r="B7" t="n">
-        <v>80351</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1307,10 +1372,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513682</v>
+        <v>513642</v>
       </c>
       <c r="R7" t="n">
-        <v>7098116</v>
+        <v>7098123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,11 +1410,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer här på en grovbarkad gammal asp med 60 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1375,14 +1435,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1400,10 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130982571</v>
+        <v>130983966</v>
       </c>
       <c r="B8" t="n">
-        <v>80351</v>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,30 +1466,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1442,10 +1493,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513700</v>
+        <v>514082</v>
       </c>
       <c r="R8" t="n">
-        <v>7098113</v>
+        <v>7097678</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,11 +1531,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer här på en grovbarkad gammal smal sälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1502,12 +1548,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1517,7 +1563,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1538,7 +1584,7 @@
         <v>130983967</v>
       </c>
       <c r="B9" t="n">
-        <v>83092</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,10 +1707,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130983931</v>
+        <v>130982556</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,50 +1718,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513518</v>
+        <v>513803</v>
       </c>
       <c r="R10" t="n">
-        <v>7098104</v>
+        <v>7097938</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,7 +1789,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I ett område med gott om aspar för bohål.</t>
+          <t>På en levande gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,12 +1798,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1784,32 +1842,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130983946</v>
+        <v>130982574</v>
       </c>
       <c r="B11" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1822,10 +1880,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513642</v>
+        <v>514157</v>
       </c>
       <c r="R11" t="n">
-        <v>7097903</v>
+        <v>7097713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1873,6 +1931,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1890,41 +1968,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130982555</v>
+        <v>130982575</v>
       </c>
       <c r="B12" t="n">
-        <v>80380</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1932,10 +2006,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513918</v>
+        <v>514100</v>
       </c>
       <c r="R12" t="n">
-        <v>7097882</v>
+        <v>7097700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,11 +2044,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer på en sälg med doftticka.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1992,22 +2061,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2025,41 +2089,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130983950</v>
+        <v>130982576</v>
       </c>
       <c r="B13" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2067,10 +2127,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513635</v>
+        <v>514066</v>
       </c>
       <c r="R13" t="n">
-        <v>7098119</v>
+        <v>7097722</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2167,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på asp och även gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,22 +2187,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2160,41 +2215,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130983949</v>
+        <v>130982577</v>
       </c>
       <c r="B14" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2202,10 +2253,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513607</v>
+        <v>514014</v>
       </c>
       <c r="R14" t="n">
-        <v>7098113</v>
+        <v>7097748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2240,11 +2291,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglavsbålar på asp.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2258,26 +2304,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2295,14 +2321,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130983965</v>
+        <v>130982578</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2333,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513657</v>
+        <v>513970</v>
       </c>
       <c r="R15" t="n">
-        <v>7098140</v>
+        <v>7097750</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2396,14 +2422,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2421,32 +2442,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130983959</v>
+        <v>130982579</v>
       </c>
       <c r="B16" t="n">
-        <v>78258</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2459,10 +2480,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513749</v>
+        <v>513930</v>
       </c>
       <c r="R16" t="n">
-        <v>7097845</v>
+        <v>7097853</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2524,12 +2545,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2547,41 +2568,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130982558</v>
+        <v>130982580</v>
       </c>
       <c r="B17" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2589,10 +2606,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513948</v>
+        <v>513904</v>
       </c>
       <c r="R17" t="n">
-        <v>7097782</v>
+        <v>7097941</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2644,22 +2661,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2677,41 +2689,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130982556</v>
+        <v>130982581</v>
       </c>
       <c r="B18" t="n">
-        <v>80352</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2719,10 +2727,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513803</v>
+        <v>513849</v>
       </c>
       <c r="R18" t="n">
-        <v>7097938</v>
+        <v>7098012</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2759,7 +2767,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en levande gammal skadad sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2779,22 +2787,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2812,61 +2820,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130983928</v>
+        <v>130982582</v>
       </c>
       <c r="B19" t="n">
-        <v>58043</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513873</v>
+        <v>513803</v>
       </c>
       <c r="R19" t="n">
-        <v>7097763</v>
+        <v>7097902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2903,7 +2898,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Fyndplats i bitvis flerskiktad gammal granskog med frekvent förekomst av murknande björkhögstubbar för talltitans bohål.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,12 +2907,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2935,14 +2946,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130982597</v>
+        <v>130982583</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2973,10 +2984,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513607</v>
+        <v>513750</v>
       </c>
       <c r="R20" t="n">
-        <v>7098058</v>
+        <v>7097880</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,9 +3047,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3056,14 +3072,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130982575</v>
+        <v>130982584</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3094,10 +3110,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514100</v>
+        <v>513738</v>
       </c>
       <c r="R21" t="n">
-        <v>7097700</v>
+        <v>7097832</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3157,9 +3173,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3177,14 +3198,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130982590</v>
+        <v>130982585</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3215,10 +3236,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513704</v>
+        <v>513767</v>
       </c>
       <c r="R22" t="n">
-        <v>7097860</v>
+        <v>7097794</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3253,6 +3274,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3278,9 +3304,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3301,11 +3332,11 @@
         <v>130982586</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3424,41 +3455,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130982567</v>
+        <v>130982587</v>
       </c>
       <c r="B24" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3466,10 +3493,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513729</v>
+        <v>513762</v>
       </c>
       <c r="R24" t="n">
-        <v>7098105</v>
+        <v>7097721</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3504,11 +3531,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav på en lutande levande sälg.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3526,22 +3548,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3559,14 +3576,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130982593</v>
+        <v>130982588</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3597,10 +3614,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513648</v>
+        <v>513723</v>
       </c>
       <c r="R25" t="n">
-        <v>7098006</v>
+        <v>7097741</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3633,6 +3650,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3680,14 +3702,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130982598</v>
+        <v>130982589</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3718,10 +3740,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513708</v>
+        <v>513732</v>
       </c>
       <c r="R26" t="n">
-        <v>7098110</v>
+        <v>7097799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3801,41 +3823,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130982568</v>
+        <v>130982590</v>
       </c>
       <c r="B27" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3843,10 +3861,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513722</v>
+        <v>513704</v>
       </c>
       <c r="R27" t="n">
-        <v>7098087</v>
+        <v>7097860</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3898,22 +3916,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3931,52 +3944,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130983944</v>
+        <v>130982591</v>
       </c>
       <c r="B28" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513823</v>
+        <v>513751</v>
       </c>
       <c r="R28" t="n">
-        <v>7097896</v>
+        <v>7097964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4013,7 +4019,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Fertil lunglav med apotechier.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4022,14 +4028,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4046,52 +4046,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130982561</v>
+        <v>130982592</v>
       </c>
       <c r="B29" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513545</v>
+        <v>513705</v>
       </c>
       <c r="R29" t="n">
-        <v>7098028</v>
+        <v>7098025</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4126,40 +4119,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4176,37 +4148,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130983963</v>
+        <v>130982593</v>
       </c>
       <c r="B30" t="n">
-        <v>91834</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4214,10 +4186,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513798</v>
+        <v>513648</v>
       </c>
       <c r="R30" t="n">
-        <v>7097846</v>
+        <v>7098006</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4297,14 +4269,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130982577</v>
+        <v>130982595</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4335,10 +4307,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514014</v>
+        <v>513525</v>
       </c>
       <c r="R31" t="n">
-        <v>7097748</v>
+        <v>7098059</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4373,6 +4345,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer på en relativt grov gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4386,6 +4363,21 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4403,14 +4395,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130982583</v>
+        <v>130982596</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4441,10 +4433,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513750</v>
+        <v>513544</v>
       </c>
       <c r="R32" t="n">
-        <v>7097880</v>
+        <v>7098021</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4479,6 +4471,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4504,14 +4501,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4529,14 +4521,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130982587</v>
+        <v>130982597</v>
       </c>
       <c r="B33" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4567,10 +4559,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513762</v>
+        <v>513607</v>
       </c>
       <c r="R33" t="n">
-        <v>7097721</v>
+        <v>7098058</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4650,14 +4642,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130982585</v>
+        <v>130982598</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4688,10 +4680,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513767</v>
+        <v>513708</v>
       </c>
       <c r="R34" t="n">
-        <v>7097794</v>
+        <v>7098110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4726,11 +4718,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4756,14 +4743,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4781,14 +4763,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130982595</v>
+        <v>130982599</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4819,10 +4801,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513525</v>
+        <v>513707</v>
       </c>
       <c r="R35" t="n">
-        <v>7098059</v>
+        <v>7098128</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4859,7 +4841,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växer på en relativt grov gran i gammal granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4907,14 +4889,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130982592</v>
+        <v>130982600</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4936,16 +4918,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513705</v>
+        <v>513799</v>
       </c>
       <c r="R36" t="n">
-        <v>7098025</v>
+        <v>7098152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4982,7 +4967,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Växer på en stående död gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4991,8 +4976,34 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5009,41 +5020,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130982559</v>
+        <v>130983965</v>
       </c>
       <c r="B37" t="n">
-        <v>80351</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5051,10 +5058,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513918</v>
+        <v>513657</v>
       </c>
       <c r="R37" t="n">
-        <v>7097882</v>
+        <v>7098140</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5089,11 +5096,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5111,22 +5113,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5144,41 +5146,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130983958</v>
+        <v>130983918</v>
       </c>
       <c r="B38" t="n">
-        <v>80387</v>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5186,10 +5184,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513915</v>
+        <v>513544</v>
       </c>
       <c r="R38" t="n">
-        <v>7097830</v>
+        <v>7098096</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5241,12 +5239,12 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -5256,7 +5254,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,10 +5272,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130982562</v>
+        <v>130982557</v>
       </c>
       <c r="B39" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5306,7 +5304,7 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5316,10 +5314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513609</v>
+        <v>514098</v>
       </c>
       <c r="R39" t="n">
-        <v>7098065</v>
+        <v>7097694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5352,11 +5350,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Fertil lunglav med apothecier på en grov tvåstammig asp i gammal granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5409,39 +5402,39 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130983930</v>
+        <v>130982558</v>
       </c>
       <c r="B40" t="n">
-        <v>91825</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5451,10 +5444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513642</v>
+        <v>513948</v>
       </c>
       <c r="R40" t="n">
-        <v>7098123</v>
+        <v>7097782</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5506,17 +5499,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5534,10 +5532,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130983956</v>
+        <v>130982559</v>
       </c>
       <c r="B41" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5564,7 +5562,11 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5572,10 +5574,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513648</v>
+        <v>513918</v>
       </c>
       <c r="R41" t="n">
-        <v>7098140</v>
+        <v>7097882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5610,6 +5612,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en gammal sälg med doftticka.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5623,6 +5630,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5640,10 +5667,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130983937</v>
+        <v>130982560</v>
       </c>
       <c r="B42" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5682,10 +5709,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513865</v>
+        <v>513804</v>
       </c>
       <c r="R42" t="n">
-        <v>7097979</v>
+        <v>7097938</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5718,6 +5745,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en levande gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5770,10 +5802,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130982565</v>
+        <v>130982561</v>
       </c>
       <c r="B43" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5800,7 +5832,11 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5808,10 +5844,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513709</v>
+        <v>513545</v>
       </c>
       <c r="R43" t="n">
-        <v>7098092</v>
+        <v>7098028</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5846,11 +5882,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Växer här på en gran intill en asp med lunglav.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5868,22 +5899,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5901,10 +5932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130982578</v>
+        <v>130982562</v>
       </c>
       <c r="B44" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5912,26 +5943,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5939,10 +5974,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513970</v>
+        <v>513609</v>
       </c>
       <c r="R44" t="n">
-        <v>7097750</v>
+        <v>7098065</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5977,6 +6012,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med apothecier på en grov tvåstammig asp i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5994,17 +6034,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6022,10 +6067,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130983960</v>
+        <v>130982563</v>
       </c>
       <c r="B45" t="n">
-        <v>91810</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6033,28 +6078,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6064,10 +6109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513513</v>
+        <v>513671</v>
       </c>
       <c r="R45" t="n">
-        <v>7098096</v>
+        <v>7098051</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6102,6 +6147,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Växer här på en grov asphögstubbe med ca 70 + cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6119,17 +6169,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6147,10 +6202,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130982600</v>
+        <v>130982564</v>
       </c>
       <c r="B46" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6158,21 +6213,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6185,10 +6240,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513799</v>
+        <v>513679</v>
       </c>
       <c r="R46" t="n">
-        <v>7098152</v>
+        <v>7098084</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6225,7 +6280,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer på en stående död gran.</t>
+          <t>Växer här på en grovbarkad asp med 64 cm i brösthöjdsdiameter (naturvärdesträd).</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6245,22 +6300,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Absolut grov bark. # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6278,10 +6333,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130983933</v>
+        <v>130982565</v>
       </c>
       <c r="B47" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6316,10 +6371,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514081</v>
+        <v>513709</v>
       </c>
       <c r="R47" t="n">
-        <v>7097679</v>
+        <v>7098092</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6354,6 +6409,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer här på en gran intill en asp med lunglav.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6371,22 +6431,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6404,10 +6464,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130983918</v>
+        <v>130982566</v>
       </c>
       <c r="B48" t="n">
-        <v>83226</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6415,26 +6475,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6442,10 +6506,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513544</v>
+        <v>513708</v>
       </c>
       <c r="R48" t="n">
-        <v>7098096</v>
+        <v>7098087</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6497,12 +6561,12 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -6512,7 +6576,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6530,10 +6594,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130983938</v>
+        <v>130982567</v>
       </c>
       <c r="B49" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6572,10 +6636,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513777</v>
+        <v>513729</v>
       </c>
       <c r="R49" t="n">
-        <v>7097981</v>
+        <v>7098105</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6610,6 +6674,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav på en lutande levande sälg.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6623,6 +6692,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6640,39 +6729,39 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130983929</v>
+        <v>130982568</v>
       </c>
       <c r="B50" t="n">
-        <v>91825</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6682,10 +6771,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513914</v>
+        <v>513722</v>
       </c>
       <c r="R50" t="n">
-        <v>7097909</v>
+        <v>7098087</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6745,9 +6834,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6765,10 +6859,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130982589</v>
+        <v>130982569</v>
       </c>
       <c r="B51" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,26 +6870,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6803,10 +6901,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513732</v>
+        <v>513717</v>
       </c>
       <c r="R51" t="n">
-        <v>7097799</v>
+        <v>7098092</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6858,17 +6956,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6886,10 +6989,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130982584</v>
+        <v>130982570</v>
       </c>
       <c r="B52" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6897,26 +7000,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6924,10 +7031,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513738</v>
+        <v>513682</v>
       </c>
       <c r="R52" t="n">
-        <v>7097832</v>
+        <v>7098116</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6962,6 +7069,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Växer här på en grovbarkad gammal asp med 60 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6979,22 +7091,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7012,10 +7124,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130982560</v>
+        <v>130982571</v>
       </c>
       <c r="B53" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7054,10 +7166,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513804</v>
+        <v>513700</v>
       </c>
       <c r="R53" t="n">
-        <v>7097938</v>
+        <v>7098113</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7094,7 +7206,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På en levande gammal skadad sälg.</t>
+          <t>Växer här på en grovbarkad gammal smal sälg.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7147,10 +7259,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130983957</v>
+        <v>130983933</v>
       </c>
       <c r="B54" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7185,10 +7297,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513674</v>
+        <v>514081</v>
       </c>
       <c r="R54" t="n">
-        <v>7098138</v>
+        <v>7097679</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7223,11 +7335,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer här på gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7245,17 +7352,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7273,10 +7385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130983941</v>
+        <v>130983935</v>
       </c>
       <c r="B55" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7303,11 +7415,7 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7315,10 +7423,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513788</v>
+        <v>513918</v>
       </c>
       <c r="R55" t="n">
-        <v>7097977</v>
+        <v>7097829</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7366,6 +7474,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7383,10 +7511,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130983951</v>
+        <v>130983936</v>
       </c>
       <c r="B56" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7413,7 +7541,11 @@
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7421,10 +7553,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513656</v>
+        <v>513887</v>
       </c>
       <c r="R56" t="n">
-        <v>7098142</v>
+        <v>7097928</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7459,11 +7591,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På björk.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7481,12 +7608,12 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -7496,7 +7623,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7514,10 +7641,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130983925</v>
+        <v>130983937</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7525,29 +7652,28 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7557,10 +7683,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513740</v>
+        <v>513865</v>
       </c>
       <c r="R57" t="n">
-        <v>7098029</v>
+        <v>7097979</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7595,17 +7721,13 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7616,22 +7738,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7649,10 +7771,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130983962</v>
+        <v>130983938</v>
       </c>
       <c r="B58" t="n">
-        <v>91834</v>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7660,24 +7782,28 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7687,10 +7813,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>514120</v>
+        <v>513777</v>
       </c>
       <c r="R58" t="n">
-        <v>7097669</v>
+        <v>7097981</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7738,21 +7864,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7770,10 +7881,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130983964</v>
+        <v>130983939</v>
       </c>
       <c r="B59" t="n">
-        <v>91834</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7781,24 +7892,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7808,10 +7923,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513717</v>
+        <v>513790</v>
       </c>
       <c r="R59" t="n">
-        <v>7098039</v>
+        <v>7097963</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7859,21 +7974,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7891,10 +7991,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130982576</v>
+        <v>130983940</v>
       </c>
       <c r="B60" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7902,21 +8002,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7929,10 +8029,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>514066</v>
+        <v>513786</v>
       </c>
       <c r="R60" t="n">
-        <v>7097722</v>
+        <v>7097956</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7967,11 +8067,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7985,21 +8080,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8017,10 +8097,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130982579</v>
+        <v>130983941</v>
       </c>
       <c r="B61" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8028,26 +8108,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8055,10 +8139,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513930</v>
+        <v>513788</v>
       </c>
       <c r="R61" t="n">
-        <v>7097853</v>
+        <v>7097977</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8106,26 +8190,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8143,10 +8207,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130982574</v>
+        <v>130983942</v>
       </c>
       <c r="B62" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8154,21 +8218,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8181,10 +8245,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>514157</v>
+        <v>513807</v>
       </c>
       <c r="R62" t="n">
-        <v>7097713</v>
+        <v>7097941</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8232,26 +8296,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8269,10 +8313,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130983922</v>
+        <v>130983943</v>
       </c>
       <c r="B63" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8280,31 +8324,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8312,10 +8351,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513814</v>
+        <v>513818</v>
       </c>
       <c r="R63" t="n">
-        <v>7097864</v>
+        <v>7097946</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8350,43 +8389,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs flera meter på en gran ca 30 m från ett gammalt bohål i en yta med mycket högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved av gran.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8404,39 +8419,39 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130983968</v>
+        <v>130983944</v>
       </c>
       <c r="B64" t="n">
-        <v>92413</v>
+        <v>80432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8446,10 +8461,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513808</v>
+        <v>513823</v>
       </c>
       <c r="R64" t="n">
-        <v>7097938</v>
+        <v>7097896</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8486,7 +8501,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 1 fruktkropp.</t>
+          <t>Fertil lunglav med apotechier.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8502,31 +8517,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>En gammal grovbarkig skadad sälg.</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea # En gammal grovbarkig skadad sälg.</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8544,10 +8534,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130982580</v>
+        <v>130983945</v>
       </c>
       <c r="B65" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8555,21 +8545,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8582,10 +8572,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513904</v>
+        <v>513618</v>
       </c>
       <c r="R65" t="n">
-        <v>7097941</v>
+        <v>7097900</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8633,21 +8623,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8665,10 +8640,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130982588</v>
+        <v>130983946</v>
       </c>
       <c r="B66" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8676,21 +8651,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8703,10 +8678,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513723</v>
+        <v>513642</v>
       </c>
       <c r="R66" t="n">
-        <v>7097741</v>
+        <v>7097903</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8741,11 +8716,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8759,21 +8729,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8791,10 +8746,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130983935</v>
+        <v>130983947</v>
       </c>
       <c r="B67" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8821,7 +8776,11 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8829,10 +8788,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513918</v>
+        <v>513666</v>
       </c>
       <c r="R67" t="n">
-        <v>7097829</v>
+        <v>7098043</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8867,6 +8826,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8884,22 +8848,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8917,10 +8881,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130983924</v>
+        <v>130983948</v>
       </c>
       <c r="B68" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8928,31 +8892,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8960,10 +8919,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513719</v>
+        <v>513581</v>
       </c>
       <c r="R68" t="n">
-        <v>7097950</v>
+        <v>7098038</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8998,43 +8957,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på tall.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9052,10 +8987,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130983919</v>
+        <v>130983949</v>
       </c>
       <c r="B69" t="n">
-        <v>91814</v>
+        <v>80432</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9063,28 +8998,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9094,10 +9029,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513795</v>
+        <v>513607</v>
       </c>
       <c r="R69" t="n">
-        <v>7097973</v>
+        <v>7098113</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9132,6 +9067,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglavsbålar på asp.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -9149,22 +9089,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9182,10 +9122,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130982599</v>
+        <v>130983950</v>
       </c>
       <c r="B70" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9193,26 +9133,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9220,10 +9164,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513707</v>
+        <v>513635</v>
       </c>
       <c r="R70" t="n">
-        <v>7098128</v>
+        <v>7098119</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9260,7 +9204,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med bålar på asp och även gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9280,17 +9224,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9308,10 +9257,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130982569</v>
+        <v>130983951</v>
       </c>
       <c r="B71" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9338,11 +9287,7 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9350,10 +9295,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513717</v>
+        <v>513656</v>
       </c>
       <c r="R71" t="n">
-        <v>7098092</v>
+        <v>7098142</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9388,6 +9333,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9405,12 +9355,12 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -9420,7 +9370,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9438,41 +9388,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130982602</v>
+        <v>130983952</v>
       </c>
       <c r="B72" t="n">
-        <v>92413</v>
+        <v>80432</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9480,10 +9426,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513918</v>
+        <v>513911</v>
       </c>
       <c r="R72" t="n">
-        <v>7097881</v>
+        <v>7097913</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9518,11 +9464,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Minst 1 fruktkropp i en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9540,22 +9481,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9573,10 +9514,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130982564</v>
+        <v>130983953</v>
       </c>
       <c r="B73" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9611,10 +9552,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513679</v>
+        <v>513845</v>
       </c>
       <c r="R73" t="n">
-        <v>7098084</v>
+        <v>7098004</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9649,11 +9590,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Växer här på en grovbarkad asp med 64 cm i brösthöjdsdiameter (naturvärdesträd).</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9671,12 +9607,12 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -9686,7 +9622,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Absolut grov bark. # Populus tremula</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9704,10 +9640,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130982566</v>
+        <v>130983954</v>
       </c>
       <c r="B74" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9746,10 +9682,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513708</v>
+        <v>513716</v>
       </c>
       <c r="R74" t="n">
-        <v>7098087</v>
+        <v>7098047</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9797,26 +9733,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9834,10 +9750,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130983927</v>
+        <v>130983955</v>
       </c>
       <c r="B75" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9845,29 +9761,28 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -9877,10 +9792,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>513553</v>
+        <v>513615</v>
       </c>
       <c r="R75" t="n">
-        <v>7097986</v>
+        <v>7098111</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9915,43 +9830,19 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9969,10 +9860,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130983936</v>
+        <v>130983956</v>
       </c>
       <c r="B76" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9999,11 +9890,7 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10011,10 +9898,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>513887</v>
+        <v>513648</v>
       </c>
       <c r="R76" t="n">
-        <v>7097928</v>
+        <v>7098140</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10062,26 +9949,6 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10099,10 +9966,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130982563</v>
+        <v>130983957</v>
       </c>
       <c r="B77" t="n">
-        <v>80351</v>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10129,11 +9996,7 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -10141,10 +10004,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>513671</v>
+        <v>513674</v>
       </c>
       <c r="R77" t="n">
-        <v>7098051</v>
+        <v>7098138</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10181,7 +10044,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Växer här på en grov asphögstubbe med ca 70 + cm i brösthöjdsdiameter.</t>
+          <t>Växer här på gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10201,22 +10064,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10234,32 +10092,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130983948</v>
+        <v>130983970</v>
       </c>
       <c r="B78" t="n">
-        <v>80351</v>
+        <v>79583</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10272,10 +10130,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>513581</v>
+        <v>513622</v>
       </c>
       <c r="R78" t="n">
-        <v>7098038</v>
+        <v>7097901</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10323,6 +10181,26 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10340,32 +10218,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130983953</v>
+        <v>130983971</v>
       </c>
       <c r="B79" t="n">
-        <v>80351</v>
+        <v>79583</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10378,10 +10256,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>513845</v>
+        <v>513579</v>
       </c>
       <c r="R79" t="n">
-        <v>7098004</v>
+        <v>7098048</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10433,12 +10311,12 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -10448,7 +10326,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10466,39 +10344,39 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130983954</v>
+        <v>130982555</v>
       </c>
       <c r="B80" t="n">
-        <v>80351</v>
+        <v>80461</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -10508,10 +10386,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>513716</v>
+        <v>513918</v>
       </c>
       <c r="R80" t="n">
-        <v>7098047</v>
+        <v>7097882</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10546,6 +10424,11 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Växer på en sälg med doftticka.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10559,6 +10442,26 @@
       <c r="AH80" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10576,37 +10479,41 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130983940</v>
+        <v>130983958</v>
       </c>
       <c r="B81" t="n">
-        <v>80351</v>
+        <v>80468</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10614,10 +10521,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>513786</v>
+        <v>513915</v>
       </c>
       <c r="R81" t="n">
-        <v>7097956</v>
+        <v>7097830</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10665,6 +10572,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10682,48 +10609,61 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130982596</v>
+        <v>130983931</v>
       </c>
       <c r="B82" t="n">
-        <v>79246</v>
+        <v>57950</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>513544</v>
+        <v>513518</v>
       </c>
       <c r="R82" t="n">
-        <v>7098021</v>
+        <v>7098104</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10760,7 +10700,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>I ett område med gott om aspar för bohål.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10769,28 +10709,12 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10808,10 +10732,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130983923</v>
+        <v>66327600</v>
       </c>
       <c r="B83" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10836,32 +10760,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
+          <t>Naturskog S Lill-Skarvhöjden, Renålandet, Ström, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>513799</v>
+        <v>514073</v>
       </c>
       <c r="R83" t="n">
-        <v>7097850</v>
+        <v>7097653</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10885,17 +10808,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2017-06-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2017-06-18</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Äldre bohål, 47-50 mm i diameter. Välsnidat och uthackat i en grantickerötad högstubbe, ca 1,8 m över marken.</t>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10906,51 +10829,26 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130982591</v>
+        <v>130983921</v>
       </c>
       <c r="B84" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10958,34 +10856,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>513751</v>
+        <v>513913</v>
       </c>
       <c r="R84" t="n">
-        <v>7097964</v>
+        <v>7097903</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11022,7 +10928,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11033,6 +10939,31 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -11049,37 +10980,42 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130983970</v>
+        <v>130983922</v>
       </c>
       <c r="B85" t="n">
-        <v>79502</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11087,10 +11023,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>513622</v>
+        <v>513814</v>
       </c>
       <c r="R85" t="n">
-        <v>7097901</v>
+        <v>7097864</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11125,13 +11061,17 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran ca 30 m från ett gammalt bohål i en yta med mycket högt livsmiljövärde för tretåig hackspett baserat på volym stående död ved av gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11142,22 +11082,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11175,10 +11115,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130982581</v>
+        <v>130983923</v>
       </c>
       <c r="B86" t="n">
-        <v>79246</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11186,37 +11126,46 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>513849</v>
+        <v>513799</v>
       </c>
       <c r="R86" t="n">
-        <v>7098012</v>
+        <v>7097850</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11253,7 +11202,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Äldre bohål, 47-50 mm i diameter. Välsnidat och uthackat i en grantickerötad högstubbe, ca 1,8 m över marken.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11262,7 +11211,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11283,12 +11231,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11306,10 +11254,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130983966</v>
+        <v>130983924</v>
       </c>
       <c r="B87" t="n">
-        <v>83092</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11317,26 +11265,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11344,10 +11297,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>514082</v>
+        <v>513719</v>
       </c>
       <c r="R87" t="n">
-        <v>7097678</v>
+        <v>7097950</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11382,13 +11335,17 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11399,22 +11356,22 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11432,10 +11389,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130982557</v>
+        <v>130983925</v>
       </c>
       <c r="B88" t="n">
-        <v>80351</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11443,28 +11400,29 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -11474,10 +11432,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>514098</v>
+        <v>513740</v>
       </c>
       <c r="R88" t="n">
-        <v>7097694</v>
+        <v>7098029</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11512,13 +11470,17 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -11529,22 +11491,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11562,10 +11524,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130983939</v>
+        <v>130983926</v>
       </c>
       <c r="B89" t="n">
-        <v>80351</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11573,28 +11535,29 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -11604,10 +11567,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>513790</v>
+        <v>513667</v>
       </c>
       <c r="R89" t="n">
-        <v>7097963</v>
+        <v>7097967</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11642,19 +11605,43 @@
           <t>2026-01-31</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -11672,10 +11659,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130983921</v>
+        <v>130983927</v>
       </c>
       <c r="B90" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11715,10 +11702,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>513913</v>
+        <v>513553</v>
       </c>
       <c r="R90" t="n">
-        <v>7097903</v>
+        <v>7097986</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11755,7 +11742,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11774,12 +11761,12 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -11789,7 +11776,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -11807,10 +11794,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130982582</v>
+        <v>130983928</v>
       </c>
       <c r="B91" t="n">
-        <v>79246</v>
+        <v>58114</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11818,37 +11805,50 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>513803</v>
+        <v>513873</v>
       </c>
       <c r="R91" t="n">
-        <v>7097902</v>
+        <v>7097763</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Fyndplats i bitvis flerskiktad gammal granskog med frekvent förekomst av murknande björkhögstubbar för talltitans bohål.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11894,28 +11894,12 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11933,10 +11917,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130983943</v>
+        <v>96280730</v>
       </c>
       <c r="B92" t="n">
-        <v>80351</v>
+        <v>102464</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11944,40 +11928,41 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>221343</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
+          <t>NA, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>513818</v>
+        <v>513973</v>
       </c>
       <c r="R92" t="n">
-        <v>7097946</v>
+        <v>7097374</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12001,12 +11986,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12015,34 +12000,32 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Tomas Axelson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130983947</v>
+        <v>130983959</v>
       </c>
       <c r="B93" t="n">
-        <v>80351</v>
+        <v>78339</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12050,30 +12033,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -12081,10 +12060,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>513666</v>
+        <v>513749</v>
       </c>
       <c r="R93" t="n">
-        <v>7098043</v>
+        <v>7097845</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12119,11 +12098,6 @@
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på gran.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -12151,12 +12125,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12171,373 +12145,6 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>130983971</v>
-      </c>
-      <c r="B94" t="n">
-        <v>79502</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>6459</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Barkkornlav</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Lopadium disciforme</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>513579</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7098048</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>130983945</v>
-      </c>
-      <c r="B95" t="n">
-        <v>80351</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>513618</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7097900</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>130983926</v>
-      </c>
-      <c r="B96" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Naturskog S Lill-Skarvhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>513667</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7097967</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63108-2025 artfynd.xlsx
+++ b/artfynd/A 63108-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -947,6 +957,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983968</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1072,6 +1087,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983960</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1202,6 +1222,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983919</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1327,6 +1352,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983929</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,6 +1482,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1578,6 +1613,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983966</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1704,6 +1744,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983967</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1839,6 +1884,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982556</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1965,6 +2015,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982574</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2086,6 +2141,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982575</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2212,6 +2272,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982576</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2318,6 +2383,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982577</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2439,6 +2509,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982578</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2565,6 +2640,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982579</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2686,6 +2766,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982580</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2817,6 +2902,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982581</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2943,6 +3033,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982582</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3069,6 +3164,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982583</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3195,6 +3295,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982584</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3326,6 +3431,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982585</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3452,6 +3562,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982586</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3573,6 +3688,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982587</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3699,6 +3819,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982588</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3820,6 +3945,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982589</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3941,6 +4071,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982590</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4043,6 +4178,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982591</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4145,6 +4285,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982592</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4266,6 +4411,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982593</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4392,6 +4542,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982595</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4518,6 +4673,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982596</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4639,6 +4799,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982597</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4760,6 +4925,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982598</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4886,6 +5056,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982599</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5017,6 +5192,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982600</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5143,6 +5323,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983965</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5269,6 +5454,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983918</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5399,6 +5589,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982557</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5529,6 +5724,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982558</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5664,6 +5864,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982559</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5799,6 +6004,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982560</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5929,6 +6139,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982561</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6064,6 +6279,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982562</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6199,6 +6419,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982563</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6330,6 +6555,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982564</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6461,6 +6691,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982565</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6591,6 +6826,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982566</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6726,6 +6966,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982567</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6856,6 +7101,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982568</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6986,6 +7236,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982569</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7121,6 +7376,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982570</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7256,6 +7516,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982571</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7382,6 +7647,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983933</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7508,6 +7778,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983935</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7638,6 +7913,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983936</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7768,6 +8048,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983937</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7878,6 +8163,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983938</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7988,6 +8278,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983939</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8094,6 +8389,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983940</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8204,6 +8504,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983941</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8310,6 +8615,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983942</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8416,6 +8726,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983943</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8531,6 +8846,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983944</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8637,6 +8957,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983945</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8743,6 +9068,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983946</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8878,6 +9208,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983947</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8984,6 +9319,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983948</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9119,6 +9459,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983949</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9254,6 +9599,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983950</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9385,6 +9735,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983951</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9511,6 +9866,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983952</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9637,6 +9997,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983953</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9747,6 +10112,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983954</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9857,6 +10227,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983955</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9963,6 +10338,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983956</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10089,6 +10469,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983957</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10215,6 +10600,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983970</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10341,6 +10731,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983971</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10476,6 +10871,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982555</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10606,6 +11006,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983958</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10729,6 +11134,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983931</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10842,6 +11252,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66327600</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10977,6 +11392,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983921</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11112,6 +11532,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983922</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11251,6 +11676,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983923</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11386,6 +11816,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983924</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11521,6 +11956,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983925</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11656,6 +12096,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983926</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11791,6 +12236,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983927</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11914,6 +12364,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983928</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12017,6 +12472,11 @@
       <c r="AY92" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96280730</t>
         </is>
       </c>
     </row>
@@ -12145,8 +12605,107 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130983959</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>